--- a/media/bookings/course_bookings.xlsx
+++ b/media/bookings/course_bookings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -841,6 +841,59 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>23-02-2026 21:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Shobana V</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>shobavelu1424@gmail.com</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>9626554049</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Full Stack Development (Example – Dynamic Based on Selection)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>4999</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>31-05-2026 20:49</t>
         </is>
       </c>
     </row>

--- a/media/bookings/course_bookings.xlsx
+++ b/media/bookings/course_bookings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -894,6 +894,59 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>31-05-2026 20:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Shobana V</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>shobavelu1424@gmail.com</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>9626554049</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Python + SQL Course Syllabus</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>emi</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1749</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1750</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>17-06-2026</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>02-06-2026 15:59</t>
         </is>
       </c>
     </row>

--- a/media/bookings/course_bookings.xlsx
+++ b/media/bookings/course_bookings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -950,6 +950,430 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Dhanusha Selvaraj</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>dhanusha.selvaraj05@gmail.com</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>09344520475</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>BCOM CA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>FRONTEND DEVELOPMENT COURSE</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>04-07-2026 15:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Dhanusha Selvaraj</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>dhanusha.selvaraj05@gmail.com</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>9344520475</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>BCOM CA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>FRONTEND DEVELOPMENT COURSE</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>04-07-2026 15:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Dhanusha Selvaraj</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>dhanusha.selvaraj05@gmail.com</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>9344520475</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>BCOM CA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>FRONTEND DEVELOPMENT COURSE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>04-07-2026 15:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Dhanusha Selvaraj</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>dhanusha.selvaraj05@gmail.com</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>9344520475</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>BCOM CA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>FRONTEND DEVELOPMENT COURSE</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>04-07-2026 15:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Dhanusha Selvaraj</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dhanusha.selvaraj05@gmail.com</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>9344520475</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BCOM CA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>FRONTEND DEVELOPMENT COURSE</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>04-07-2026 15:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Dhanusha Selvaraj</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>dhanusha.selvaraj05@gmail.com</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>9344520475</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BCOM CA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>PYTHON + SQL COURSE</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>04-07-2026 16:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Dhanusha Selvaraj</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>dhanusha.selvaraj05@gmail.com</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>9344520475</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BCOM CA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>PYTHON + SQL COURSE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>04-07-2026 16:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>gopika</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>gopikas04082005@gmail.com</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>82483464453</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>bsc com</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>FRONTEND DEVELOPMENT COURSE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>04-07-2026 17:28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/media/bookings/course_bookings.xlsx
+++ b/media/bookings/course_bookings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1374,6 +1374,112 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Dhanusha Selvaraj</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>dhanusha.selvaraj05@gmail.com</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>09344520475</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>BCOM CA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>PYTHON + SQL COURSE</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>06-07-2026 16:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Dhanusha Selvaraj</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>dhanusha.selvaraj05@gmail.com</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>09344520475</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>BCOM CA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>PYTHON + SQL COURSE</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>06-07-2026 16:19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
